--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/67.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/67.xlsx
@@ -426,13 +426,13 @@
         <v>-2.753104763871204</v>
       </c>
       <c r="E2">
-        <v>-5.838658712751155</v>
+        <v>-6.008829709011391</v>
       </c>
       <c r="F2">
-        <v>-5.235613479901503</v>
+        <v>-5.481892078958213</v>
       </c>
       <c r="G2">
-        <v>-9.443418375623416</v>
+        <v>-9.419834049201649</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.696411217383137</v>
       </c>
       <c r="E3">
-        <v>-6.872663296818558</v>
+        <v>-5.638377892813918</v>
       </c>
       <c r="F3">
-        <v>-4.957599297276142</v>
+        <v>-5.460625402626141</v>
       </c>
       <c r="G3">
-        <v>-9.767289045730315</v>
+        <v>-9.591095191039225</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.769660838669064</v>
       </c>
       <c r="E4">
-        <v>-6.670503160168138</v>
+        <v>-7.261034284664383</v>
       </c>
       <c r="F4">
-        <v>-4.860964441167759</v>
+        <v>-5.201976793143427</v>
       </c>
       <c r="G4">
-        <v>-10.47686806607216</v>
+        <v>-9.107023911741454</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.960965879197416</v>
       </c>
       <c r="E5">
-        <v>-7.628212014154311</v>
+        <v>-7.113967562791281</v>
       </c>
       <c r="F5">
-        <v>-4.744190316762516</v>
+        <v>-5.216114539607005</v>
       </c>
       <c r="G5">
-        <v>-10.28139028361482</v>
+        <v>-10.32290452467728</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.241859244948611</v>
       </c>
       <c r="E6">
-        <v>-7.451755495971428</v>
+        <v>-8.051646976241528</v>
       </c>
       <c r="F6">
-        <v>-4.3169092983571</v>
+        <v>-4.930165425630228</v>
       </c>
       <c r="G6">
-        <v>-10.92542712337017</v>
+        <v>-10.86755216625263</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.581503326072656</v>
       </c>
       <c r="E7">
-        <v>-9.054631513356389</v>
+        <v>-7.333743463331539</v>
       </c>
       <c r="F7">
-        <v>-3.894582745387828</v>
+        <v>-4.431246365863307</v>
       </c>
       <c r="G7">
-        <v>-10.82605447791787</v>
+        <v>-11.5487068425943</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.944137145909241</v>
       </c>
       <c r="E8">
-        <v>-8.694056298969645</v>
+        <v>-7.07931115121058</v>
       </c>
       <c r="F8">
-        <v>-3.875726618197903</v>
+        <v>-4.111012781819463</v>
       </c>
       <c r="G8">
-        <v>-11.7140685922809</v>
+        <v>-11.3896251977957</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.300408857523874</v>
       </c>
       <c r="E9">
-        <v>-9.881820689493487</v>
+        <v>-8.443183367418715</v>
       </c>
       <c r="F9">
-        <v>-3.593783488981063</v>
+        <v>-4.10417046707234</v>
       </c>
       <c r="G9">
-        <v>-10.61441130159226</v>
+        <v>-11.71933898077942</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.618522487709696</v>
       </c>
       <c r="E10">
-        <v>-9.774332830447424</v>
+        <v>-8.369323956353611</v>
       </c>
       <c r="F10">
-        <v>-3.225980906831458</v>
+        <v>-3.768816692825196</v>
       </c>
       <c r="G10">
-        <v>-11.52025270368426</v>
+        <v>-12.25150255512618</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.878118651862757</v>
       </c>
       <c r="E11">
-        <v>-9.882336935530363</v>
+        <v>-9.919026631940508</v>
       </c>
       <c r="F11">
-        <v>-3.228832975799296</v>
+        <v>-3.388055131026195</v>
       </c>
       <c r="G11">
-        <v>-12.3556821127015</v>
+        <v>-12.84786091802495</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.06519550523919</v>
       </c>
       <c r="E12">
-        <v>-10.22809951143802</v>
+        <v>-10.69495348231078</v>
       </c>
       <c r="F12">
-        <v>-2.711756930930414</v>
+        <v>-3.118361898961954</v>
       </c>
       <c r="G12">
-        <v>-12.05745161779626</v>
+        <v>-12.17020879886384</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.17190899773498</v>
       </c>
       <c r="E13">
-        <v>-10.72122768850328</v>
+        <v>-10.14005691978089</v>
       </c>
       <c r="F13">
-        <v>-2.478029754760922</v>
+        <v>-2.713467509617195</v>
       </c>
       <c r="G13">
-        <v>-11.79900394863644</v>
+        <v>-11.67246827703441</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.204018967782091</v>
       </c>
       <c r="E14">
-        <v>-11.03163193935904</v>
+        <v>-10.23991882859804</v>
       </c>
       <c r="F14">
-        <v>-2.554703441564045</v>
+        <v>-2.335249035744789</v>
       </c>
       <c r="G14">
-        <v>-11.79249872665177</v>
+        <v>-12.09362263835834</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.168086348074289</v>
       </c>
       <c r="E15">
-        <v>-10.7720688661874</v>
+        <v>-11.24628160732262</v>
       </c>
       <c r="F15">
-        <v>-1.815184241286606</v>
+        <v>-2.426163186569437</v>
       </c>
       <c r="G15">
-        <v>-11.79264770120104</v>
+        <v>-12.06966422029063</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.079200384095596</v>
       </c>
       <c r="E16">
-        <v>-11.73736291413642</v>
+        <v>-11.33373549735875</v>
       </c>
       <c r="F16">
-        <v>-1.872470817394608</v>
+        <v>-2.089449233046897</v>
       </c>
       <c r="G16">
-        <v>-11.8126996755324</v>
+        <v>-11.10025703329909</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.950254908052017</v>
       </c>
       <c r="E17">
-        <v>-13.49213753516067</v>
+        <v>-12.74655146064179</v>
       </c>
       <c r="F17">
-        <v>-1.442590382079208</v>
+        <v>-2.065315577133736</v>
       </c>
       <c r="G17">
-        <v>-11.2756265621509</v>
+        <v>-11.02855392746401</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.793576136573445</v>
       </c>
       <c r="E18">
-        <v>-13.70983033765739</v>
+        <v>-13.3300362795821</v>
       </c>
       <c r="F18">
-        <v>-1.240319629663624</v>
+        <v>-1.529245896086064</v>
       </c>
       <c r="G18">
-        <v>-10.6605934118651</v>
+        <v>-10.18492098660045</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.627314023816547</v>
       </c>
       <c r="E19">
-        <v>-15.04142811961286</v>
+        <v>-13.92907187826475</v>
       </c>
       <c r="F19">
-        <v>-1.271339503796257</v>
+        <v>-1.32626771790849</v>
       </c>
       <c r="G19">
-        <v>-10.26092449109104</v>
+        <v>-9.353864808240591</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.462740918236554</v>
       </c>
       <c r="E20">
-        <v>-14.47458544265074</v>
+        <v>-13.65298893191312</v>
       </c>
       <c r="F20">
-        <v>-0.9691311944373305</v>
+        <v>-1.114570972816451</v>
       </c>
       <c r="G20">
-        <v>-9.486697137458309</v>
+        <v>-9.698151612688177</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.318820980310821</v>
       </c>
       <c r="E21">
-        <v>-15.35829450287757</v>
+        <v>-15.82839086113982</v>
       </c>
       <c r="F21">
-        <v>-0.9568804689173287</v>
+        <v>-0.814561150544554</v>
       </c>
       <c r="G21">
-        <v>-7.897324087327447</v>
+        <v>-8.468916259046932</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.209958339214016</v>
       </c>
       <c r="E22">
-        <v>-16.89318906845939</v>
+        <v>-16.1294121138517</v>
       </c>
       <c r="F22">
-        <v>-0.3703043989535679</v>
+        <v>-1.208371984039856</v>
       </c>
       <c r="G22">
-        <v>-8.01073344586626</v>
+        <v>-7.938583416383384</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.148206592744938</v>
       </c>
       <c r="E23">
-        <v>-17.65732830098769</v>
+        <v>-16.25749547268465</v>
       </c>
       <c r="F23">
-        <v>-0.2315329781669836</v>
+        <v>-0.8789899103994939</v>
       </c>
       <c r="G23">
-        <v>-7.625097927633178</v>
+        <v>-7.857577677582957</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.147720976470406</v>
       </c>
       <c r="E24">
-        <v>-17.32926300150201</v>
+        <v>-17.4900147718263</v>
       </c>
       <c r="F24">
-        <v>-0.2674369065065225</v>
+        <v>-0.5788077877078147</v>
       </c>
       <c r="G24">
-        <v>-7.339020445402597</v>
+        <v>-7.002774956069901</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.207670909870165</v>
       </c>
       <c r="E25">
-        <v>-18.14067044572238</v>
+        <v>-18.24776885600378</v>
       </c>
       <c r="F25">
-        <v>-0.2495226330535804</v>
+        <v>-0.8292688137812593</v>
       </c>
       <c r="G25">
-        <v>-7.672346033569656</v>
+        <v>-6.88440640031326</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.333926150316004</v>
       </c>
       <c r="E26">
-        <v>-18.41640469957542</v>
+        <v>-17.52470288272505</v>
       </c>
       <c r="F26">
-        <v>-0.1002392299254703</v>
+        <v>-0.6199718490551306</v>
       </c>
       <c r="G26">
-        <v>-6.755017038456384</v>
+        <v>-6.91801836917348</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.523241987910845</v>
       </c>
       <c r="E27">
-        <v>-19.63421098666615</v>
+        <v>-18.4227128638681</v>
       </c>
       <c r="F27">
-        <v>-0.2969334129854073</v>
+        <v>-0.5426429236363939</v>
       </c>
       <c r="G27">
-        <v>-6.361850029121459</v>
+        <v>-6.177409605492044</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.770319999636582</v>
       </c>
       <c r="E28">
-        <v>-18.73228387550646</v>
+        <v>-18.17356075244009</v>
       </c>
       <c r="F28">
-        <v>-0.6952538786215496</v>
+        <v>-0.7900704682807866</v>
       </c>
       <c r="G28">
-        <v>-7.170430913815212</v>
+        <v>-6.63352663825621</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.071290537573521</v>
       </c>
       <c r="E29">
-        <v>-19.40517888525421</v>
+        <v>-17.8636138774591</v>
       </c>
       <c r="F29">
-        <v>-0.7145159058388465</v>
+        <v>-0.7711041682262891</v>
       </c>
       <c r="G29">
-        <v>-6.451625403055416</v>
+        <v>-7.348584611465552</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.406871087858845</v>
       </c>
       <c r="E30">
-        <v>-18.84660520183009</v>
+        <v>-17.64790001810372</v>
       </c>
       <c r="F30">
-        <v>-0.7026338038130904</v>
+        <v>-0.9752346054611574</v>
       </c>
       <c r="G30">
-        <v>-6.678973807419325</v>
+        <v>-5.90416048722614</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.766251730087888</v>
       </c>
       <c r="E31">
-        <v>-18.34887156669903</v>
+        <v>-18.08545929062086</v>
       </c>
       <c r="F31">
-        <v>-0.8857460749367267</v>
+        <v>-1.389920297507007</v>
       </c>
       <c r="G31">
-        <v>-5.948323164720017</v>
+        <v>-6.717270198217615</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.128292366140926</v>
       </c>
       <c r="E32">
-        <v>-19.31044320901375</v>
+        <v>-18.51028449422843</v>
       </c>
       <c r="F32">
-        <v>-1.192662824613166</v>
+        <v>-1.509006395333464</v>
       </c>
       <c r="G32">
-        <v>-6.537928014718677</v>
+        <v>-6.2135872471452</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.470909783143131</v>
       </c>
       <c r="E33">
-        <v>-18.50048940494984</v>
+        <v>-17.90616341923517</v>
       </c>
       <c r="F33">
-        <v>-1.233005973864308</v>
+        <v>-1.191335780033881</v>
       </c>
       <c r="G33">
-        <v>-5.876547226883079</v>
+        <v>-6.137997560847021</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.774861523912658</v>
       </c>
       <c r="E34">
-        <v>-18.03644308796184</v>
+        <v>-17.97457054759504</v>
       </c>
       <c r="F34">
-        <v>-1.275277562429166</v>
+        <v>-1.080911091771096</v>
       </c>
       <c r="G34">
-        <v>-6.797829013370239</v>
+        <v>-6.333170773114754</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.019935158203109</v>
       </c>
       <c r="E35">
-        <v>-17.10671567486906</v>
+        <v>-17.55420589088502</v>
       </c>
       <c r="F35">
-        <v>-0.8888963561695732</v>
+        <v>-1.392928099546572</v>
       </c>
       <c r="G35">
-        <v>-6.638631499477767</v>
+        <v>-6.486439099946391</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.200848785835155</v>
       </c>
       <c r="E36">
-        <v>-17.71211377953249</v>
+        <v>-17.30590513257045</v>
       </c>
       <c r="F36">
-        <v>-0.8880688171341765</v>
+        <v>-1.520838795315052</v>
       </c>
       <c r="G36">
-        <v>-6.586874430516801</v>
+        <v>-6.828418454153105</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.310164615203793</v>
       </c>
       <c r="E37">
-        <v>-17.3618453719872</v>
+        <v>-16.56046396921981</v>
       </c>
       <c r="F37">
-        <v>-1.493656747359589</v>
+        <v>-1.878203119821981</v>
       </c>
       <c r="G37">
-        <v>-6.273286314854877</v>
+        <v>-5.948680703638258</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.34790147301559</v>
       </c>
       <c r="E38">
-        <v>-16.94672921665207</v>
+        <v>-16.30661583024585</v>
       </c>
       <c r="F38">
-        <v>-1.050073458467079</v>
+        <v>-1.454660523505399</v>
       </c>
       <c r="G38">
-        <v>-5.950964980060355</v>
+        <v>-5.930442908262414</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.317368827752667</v>
       </c>
       <c r="E39">
-        <v>-15.75312762313234</v>
+        <v>-17.42364545676988</v>
       </c>
       <c r="F39">
-        <v>-1.355589438865384</v>
+        <v>-1.165136175818138</v>
       </c>
       <c r="G39">
-        <v>-5.754835020131774</v>
+        <v>-6.442620719188598</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.217285800981381</v>
       </c>
       <c r="E40">
-        <v>-16.47748421150326</v>
+        <v>-15.82725874263791</v>
       </c>
       <c r="F40">
-        <v>-1.140679456617886</v>
+        <v>-1.642293195546112</v>
       </c>
       <c r="G40">
-        <v>-5.835807653476808</v>
+        <v>-6.403466897095638</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.056061664444506</v>
       </c>
       <c r="E41">
-        <v>-16.21760414515108</v>
+        <v>-15.5677771819984</v>
       </c>
       <c r="F41">
-        <v>-1.179535686381002</v>
+        <v>-1.809039411892639</v>
       </c>
       <c r="G41">
-        <v>-4.739884658156474</v>
+        <v>-5.667900094270512</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.837679811226523</v>
       </c>
       <c r="E42">
-        <v>-15.57310266743142</v>
+        <v>-15.28708877758096</v>
       </c>
       <c r="F42">
-        <v>-1.326971001833467</v>
+        <v>-1.403889885387817</v>
       </c>
       <c r="G42">
-        <v>-5.271349707394452</v>
+        <v>-5.712993035060925</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.569891546931016</v>
       </c>
       <c r="E43">
-        <v>-16.01220162111116</v>
+        <v>-15.27991114627881</v>
       </c>
       <c r="F43">
-        <v>-1.318003096330759</v>
+        <v>-1.215655818612672</v>
       </c>
       <c r="G43">
-        <v>-5.701753732955099</v>
+        <v>-5.732915898116259</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.262768669725554</v>
       </c>
       <c r="E44">
-        <v>-14.38268006266507</v>
+        <v>-14.45902107748638</v>
       </c>
       <c r="F44">
-        <v>-1.407598486250151</v>
+        <v>-1.718980964595082</v>
       </c>
       <c r="G44">
-        <v>-5.813713072547712</v>
+        <v>-5.306554048659062</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.918702169365258</v>
       </c>
       <c r="E45">
-        <v>-14.66231786111272</v>
+        <v>-14.45266309997961</v>
       </c>
       <c r="F45">
-        <v>-0.8270711550616321</v>
+        <v>-1.454204921433859</v>
       </c>
       <c r="G45">
-        <v>-5.274349061653032</v>
+        <v>-5.08121514543749</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.549260621718435</v>
       </c>
       <c r="E46">
-        <v>-14.03415058913873</v>
+        <v>-13.98901528870428</v>
       </c>
       <c r="F46">
-        <v>-1.569155809185541</v>
+        <v>-1.779199961308995</v>
       </c>
       <c r="G46">
-        <v>-4.76261486382911</v>
+        <v>-5.052761006527454</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.158087417782371</v>
       </c>
       <c r="E47">
-        <v>-15.05730494948376</v>
+        <v>-14.01090593205736</v>
       </c>
       <c r="F47">
-        <v>-1.043531841087171</v>
+        <v>-1.870910173207734</v>
       </c>
       <c r="G47">
-        <v>-4.192826939428528</v>
+        <v>-4.457942047304443</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.752529441978598</v>
       </c>
       <c r="E48">
-        <v>-14.37695154304537</v>
+        <v>-13.50600825104616</v>
       </c>
       <c r="F48">
-        <v>-1.454663008607608</v>
+        <v>-1.630859240285271</v>
       </c>
       <c r="G48">
-        <v>-4.073749926926483</v>
+        <v>-4.901048636099274</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.342280825986414</v>
       </c>
       <c r="E49">
-        <v>-13.59071788583364</v>
+        <v>-12.82605787879445</v>
       </c>
       <c r="F49">
-        <v>-1.612075181059389</v>
+        <v>-2.215822478915781</v>
       </c>
       <c r="G49">
-        <v>-4.92087218278843</v>
+        <v>-4.333064959017594</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.929869669078806</v>
       </c>
       <c r="E50">
-        <v>-13.67582149785979</v>
+        <v>-12.67839792682635</v>
       </c>
       <c r="F50">
-        <v>-1.650235582204154</v>
+        <v>-1.981257823302059</v>
       </c>
       <c r="G50">
-        <v>-4.849788148969199</v>
+        <v>-4.516545324440622</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.527408428656368</v>
       </c>
       <c r="E51">
-        <v>-12.73484535533196</v>
+        <v>-12.89450576342039</v>
       </c>
       <c r="F51">
-        <v>-1.680195146061204</v>
+        <v>-1.932969802290667</v>
       </c>
       <c r="G51">
-        <v>-3.60444368073386</v>
+        <v>-3.972228737419192</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.140693095526555</v>
       </c>
       <c r="E52">
-        <v>-12.79290039211029</v>
+        <v>-12.01293867139919</v>
       </c>
       <c r="F52">
-        <v>-1.857665406804373</v>
+        <v>-1.951800250091106</v>
       </c>
       <c r="G52">
-        <v>-4.371374591998041</v>
+        <v>-4.517386203007597</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.778767405561516</v>
       </c>
       <c r="E53">
-        <v>-12.46629326125508</v>
+        <v>-11.9707332936477</v>
       </c>
       <c r="F53">
-        <v>-1.909839299302297</v>
+        <v>-2.073001998264313</v>
       </c>
       <c r="G53">
-        <v>-4.131671231681572</v>
+        <v>-4.164273484152314</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.451025611396112</v>
       </c>
       <c r="E54">
-        <v>-11.42829456311292</v>
+        <v>-12.43357956502367</v>
       </c>
       <c r="F54">
-        <v>-1.745857344978912</v>
+        <v>-2.016085702385361</v>
       </c>
       <c r="G54">
-        <v>-4.653015943205998</v>
+        <v>-4.54857485253307</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.157751555450676</v>
       </c>
       <c r="E55">
-        <v>-12.07473422770786</v>
+        <v>-11.46950820505672</v>
       </c>
       <c r="F55">
-        <v>-2.198115297313539</v>
+        <v>-1.786277532398514</v>
       </c>
       <c r="G55">
-        <v>-3.878268833923598</v>
+        <v>-4.426829540326373</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.902247583427848</v>
       </c>
       <c r="E56">
-        <v>-11.76617306577322</v>
+        <v>-11.77691460611941</v>
       </c>
       <c r="F56">
-        <v>-2.046027870526952</v>
+        <v>-1.842811122537372</v>
       </c>
       <c r="G56">
-        <v>-5.319759814815215</v>
+        <v>-4.052979564213095</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.68032645686448</v>
       </c>
       <c r="E57">
-        <v>-11.97962268812476</v>
+        <v>-10.59955212039119</v>
       </c>
       <c r="F57">
-        <v>-1.847006803432552</v>
+        <v>-2.33141452303723</v>
       </c>
       <c r="G57">
-        <v>-4.404648885213255</v>
+        <v>-4.16515077872022</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.491562528728842</v>
       </c>
       <c r="E58">
-        <v>-11.4316501623526</v>
+        <v>-9.375537295435942</v>
       </c>
       <c r="F58">
-        <v>-1.913438555667461</v>
+        <v>-2.067076686232088</v>
       </c>
       <c r="G58">
-        <v>-4.97701572458893</v>
+        <v>-4.582742993043889</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.336824228456702</v>
       </c>
       <c r="E59">
-        <v>-11.10642874454374</v>
+        <v>-10.00244112316179</v>
       </c>
       <c r="F59">
-        <v>-1.917093312648612</v>
+        <v>-2.173880580577237</v>
       </c>
       <c r="G59">
-        <v>-4.704753148893728</v>
+        <v>-5.93459102182312</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.212501110982136</v>
       </c>
       <c r="E60">
-        <v>-10.72455158842491</v>
+        <v>-10.05164299325513</v>
       </c>
       <c r="F60">
-        <v>-1.938182718356485</v>
+        <v>-2.152487992399939</v>
       </c>
       <c r="G60">
-        <v>-4.672620993889562</v>
+        <v>-4.260421658249367</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.119725809989578</v>
       </c>
       <c r="E61">
-        <v>-11.20911189266766</v>
+        <v>-9.65743933088743</v>
       </c>
       <c r="F61">
-        <v>-2.033691823164462</v>
+        <v>-2.20078761055497</v>
       </c>
       <c r="G61">
-        <v>-5.614444715447901</v>
+        <v>-5.210117857100093</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.055548840963742</v>
       </c>
       <c r="E62">
-        <v>-10.65876191804148</v>
+        <v>-10.13280683289461</v>
       </c>
       <c r="F62">
-        <v>-1.980325909973909</v>
+        <v>-2.327284283166871</v>
       </c>
       <c r="G62">
-        <v>-5.561224385358576</v>
+        <v>-5.516985565317296</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.020913520204628</v>
       </c>
       <c r="E63">
-        <v>-10.01313285029391</v>
+        <v>-9.526865311350262</v>
       </c>
       <c r="F63">
-        <v>-1.985764970340691</v>
+        <v>-2.586492869013878</v>
       </c>
       <c r="G63">
-        <v>-6.033692202541204</v>
+        <v>-5.324202566928917</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.014928182535217</v>
       </c>
       <c r="E64">
-        <v>-10.43742369396857</v>
+        <v>-9.433076086177401</v>
       </c>
       <c r="F64">
-        <v>-1.639184332683406</v>
+        <v>-2.242913406456936</v>
       </c>
       <c r="G64">
-        <v>-5.819410521420798</v>
+        <v>-5.773251584966739</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.035735911790297</v>
       </c>
       <c r="E65">
-        <v>-9.907107688352319</v>
+        <v>-9.625762655203776</v>
       </c>
       <c r="F65">
-        <v>-2.16241266225288</v>
+        <v>-2.476269474029973</v>
       </c>
       <c r="G65">
-        <v>-6.321991060828635</v>
+        <v>-5.364121125041449</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.082349558021842</v>
       </c>
       <c r="E66">
-        <v>-10.98638795554841</v>
+        <v>-10.72171676369611</v>
       </c>
       <c r="F66">
-        <v>-2.191268012361998</v>
+        <v>-2.68148838603212</v>
       </c>
       <c r="G66">
-        <v>-5.653843517910767</v>
+        <v>-5.588215263140254</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.149842575359441</v>
       </c>
       <c r="E67">
-        <v>-11.06263387241556</v>
+        <v>-10.22918634519986</v>
       </c>
       <c r="F67">
-        <v>-2.04719006999308</v>
+        <v>-2.266780328066395</v>
       </c>
       <c r="G67">
-        <v>-6.486968787232676</v>
+        <v>-5.27699418753891</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.236218641993595</v>
       </c>
       <c r="E68">
-        <v>-10.07955197856441</v>
+        <v>-10.11006483642809</v>
       </c>
       <c r="F68">
-        <v>-1.70478026220889</v>
+        <v>-2.796138576416586</v>
       </c>
       <c r="G68">
-        <v>-5.661375009012609</v>
+        <v>-5.232665982768069</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.335902693001004</v>
       </c>
       <c r="E69">
-        <v>-10.58891473494717</v>
+        <v>-9.6777314229158</v>
       </c>
       <c r="F69">
-        <v>-1.96027610535655</v>
+        <v>-2.49833055470133</v>
       </c>
       <c r="G69">
-        <v>-6.468413179485061</v>
+        <v>-6.012431879088004</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.442613875664753</v>
       </c>
       <c r="E70">
-        <v>-11.25667445517022</v>
+        <v>-9.199384185011573</v>
       </c>
       <c r="F70">
-        <v>-2.342302584179626</v>
+        <v>-2.706830629985965</v>
       </c>
       <c r="G70">
-        <v>-6.549399055012251</v>
+        <v>-5.762843229791271</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.548859741128805</v>
       </c>
       <c r="E71">
-        <v>-10.85105450982918</v>
+        <v>-9.950970487590615</v>
       </c>
       <c r="F71">
-        <v>-1.955846824853781</v>
+        <v>-2.703792178352497</v>
       </c>
       <c r="G71">
-        <v>-6.237416553936874</v>
+        <v>-5.572351128916067</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.64539072483321</v>
       </c>
       <c r="E72">
-        <v>-11.04413052762022</v>
+        <v>-10.62420966136295</v>
       </c>
       <c r="F72">
-        <v>-1.982692555643708</v>
+        <v>-2.921396011393899</v>
       </c>
       <c r="G72">
-        <v>-6.437777391064644</v>
+        <v>-5.98869526757143</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.725664908114601</v>
       </c>
       <c r="E73">
-        <v>-10.83470671866149</v>
+        <v>-10.77904271615921</v>
       </c>
       <c r="F73">
-        <v>-2.03072626786244</v>
+        <v>-2.508072155358252</v>
       </c>
       <c r="G73">
-        <v>-4.986331599736439</v>
+        <v>-6.036840531349051</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.782927051104049</v>
       </c>
       <c r="E74">
-        <v>-12.75631937907633</v>
+        <v>-10.62956684611403</v>
       </c>
       <c r="F74">
-        <v>-2.152714965068306</v>
+        <v>-3.08540944367859</v>
       </c>
       <c r="G74">
-        <v>-5.763604655265303</v>
+        <v>-5.735862283646211</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.812847249854586</v>
       </c>
       <c r="E75">
-        <v>-12.23757362454968</v>
+        <v>-10.06371137648557</v>
       </c>
       <c r="F75">
-        <v>-2.329194498397727</v>
+        <v>-2.84385916575706</v>
       </c>
       <c r="G75">
-        <v>-5.725741945932659</v>
+        <v>-5.688816120987628</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.813556709756858</v>
       </c>
       <c r="E76">
-        <v>-12.34174664062213</v>
+        <v>-11.28642200092661</v>
       </c>
       <c r="F76">
-        <v>-2.190652535381718</v>
+        <v>-3.209518761435623</v>
       </c>
       <c r="G76">
-        <v>-5.448301677014037</v>
+        <v>-5.019705209317832</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.782941395896689</v>
       </c>
       <c r="E77">
-        <v>-12.36213835907867</v>
+        <v>-12.12468782448647</v>
       </c>
       <c r="F77">
-        <v>-2.12983131556597</v>
+        <v>-3.182704508607003</v>
       </c>
       <c r="G77">
-        <v>-5.251771141075203</v>
+        <v>-5.200341816122624</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.722823491955445</v>
       </c>
       <c r="E78">
-        <v>-13.39930834647743</v>
+        <v>-12.5531493927222</v>
       </c>
       <c r="F78">
-        <v>-2.621076379713355</v>
+        <v>-3.106019224660242</v>
       </c>
       <c r="G78">
-        <v>-5.71419807363722</v>
+        <v>-4.985305330619265</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.634499541650464</v>
       </c>
       <c r="E79">
-        <v>-13.76514111918708</v>
+        <v>-12.94234909131143</v>
       </c>
       <c r="F79">
-        <v>-2.174438071839321</v>
+        <v>-3.099497488098001</v>
       </c>
       <c r="G79">
-        <v>-5.138043970164619</v>
+        <v>-5.135210143183003</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.519348518357367</v>
       </c>
       <c r="E80">
-        <v>-15.00946162159272</v>
+        <v>-13.73661173293876</v>
       </c>
       <c r="F80">
-        <v>-2.499808362147924</v>
+        <v>-3.495457106636165</v>
       </c>
       <c r="G80">
-        <v>-4.154146525347683</v>
+        <v>-4.127049710108749</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.381777907715054</v>
       </c>
       <c r="E81">
-        <v>-14.90016237294359</v>
+        <v>-13.55167791141352</v>
       </c>
       <c r="F81">
-        <v>-2.558529670597576</v>
+        <v>-3.015717237346262</v>
       </c>
       <c r="G81">
-        <v>-4.533667465969732</v>
+        <v>-4.394075002760824</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.225963847012559</v>
       </c>
       <c r="E82">
-        <v>-16.51843067348062</v>
+        <v>-13.83761934567984</v>
       </c>
       <c r="F82">
-        <v>-2.147146679386688</v>
+        <v>-3.3534070076693</v>
       </c>
       <c r="G82">
-        <v>-4.137289227461714</v>
+        <v>-4.047341705159717</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.059414429545533</v>
       </c>
       <c r="E83">
-        <v>-17.84852047359153</v>
+        <v>-15.86543830699658</v>
       </c>
       <c r="F83">
-        <v>-2.598922521892885</v>
+        <v>-3.553656543622052</v>
       </c>
       <c r="G83">
-        <v>-4.018579685514529</v>
+        <v>-3.055412876864509</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.888665962916683</v>
       </c>
       <c r="E84">
-        <v>-18.59821387403537</v>
+        <v>-16.60000660425479</v>
       </c>
       <c r="F84">
-        <v>-2.707889283526743</v>
+        <v>-3.625848762776029</v>
       </c>
       <c r="G84">
-        <v>-4.111632499532363</v>
+        <v>-3.470813510041178</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.7220124619409511</v>
       </c>
       <c r="E85">
-        <v>-18.02814239510578</v>
+        <v>-17.40024230309824</v>
       </c>
       <c r="F85">
-        <v>-2.658092805474854</v>
+        <v>-3.754609363499782</v>
       </c>
       <c r="G85">
-        <v>-4.365498373665835</v>
+        <v>-3.164482110201337</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.5689611964431478</v>
       </c>
       <c r="E86">
-        <v>-20.15854487811827</v>
+        <v>-17.83017109691245</v>
       </c>
       <c r="F86">
-        <v>-3.032216659275222</v>
+        <v>-3.599426327728934</v>
       </c>
       <c r="G86">
-        <v>-3.912185372973431</v>
+        <v>-3.182325950658009</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.4379976089673849</v>
       </c>
       <c r="E87">
-        <v>-20.89971569047967</v>
+        <v>-20.02391334587023</v>
       </c>
       <c r="F87">
-        <v>-2.862528081913952</v>
+        <v>-3.559087320314806</v>
       </c>
       <c r="G87">
-        <v>-3.487981999207839</v>
+        <v>-3.02983229148256</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.3396844293822597</v>
       </c>
       <c r="E88">
-        <v>-22.82787199583559</v>
+        <v>-20.98448872390325</v>
       </c>
       <c r="F88">
-        <v>-2.962323159664014</v>
+        <v>-3.845128383073295</v>
       </c>
       <c r="G88">
-        <v>-4.136544354715379</v>
+        <v>-3.054426334293805</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.2795950146612669</v>
       </c>
       <c r="E89">
-        <v>-23.89614354271903</v>
+        <v>-21.84809135953603</v>
       </c>
       <c r="F89">
-        <v>-3.237286465144865</v>
+        <v>-3.714000308312341</v>
       </c>
       <c r="G89">
-        <v>-3.585762272255753</v>
+        <v>-3.027557946697081</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.2649272837747033</v>
       </c>
       <c r="E90">
-        <v>-25.64948263748285</v>
+        <v>-24.28525720030212</v>
       </c>
       <c r="F90">
-        <v>-3.03256208848219</v>
+        <v>-3.759241594016236</v>
       </c>
       <c r="G90">
-        <v>-3.251248198240095</v>
+        <v>-3.461504255984748</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.3006374204876813</v>
       </c>
       <c r="E91">
-        <v>-26.30210819757227</v>
+        <v>-25.22267396225992</v>
       </c>
       <c r="F91">
-        <v>-3.447889765265209</v>
+        <v>-4.028930684243464</v>
       </c>
       <c r="G91">
-        <v>-3.631586843610344</v>
+        <v>-3.17832350110103</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.3919348043096073</v>
       </c>
       <c r="E92">
-        <v>-28.43358845739859</v>
+        <v>-27.27294056923267</v>
       </c>
       <c r="F92">
-        <v>-3.120709492181488</v>
+        <v>-4.112758980304565</v>
       </c>
       <c r="G92">
-        <v>-3.036029632732076</v>
+        <v>-3.349760101852188</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.5452909137985735</v>
       </c>
       <c r="E93">
-        <v>-30.54359242924352</v>
+        <v>-29.29912022295863</v>
       </c>
       <c r="F93">
-        <v>-2.905271011531004</v>
+        <v>-3.724807189449264</v>
       </c>
       <c r="G93">
-        <v>-3.584795592958285</v>
+        <v>-3.930343715256333</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.7614556798045254</v>
       </c>
       <c r="E94">
-        <v>-32.52421337021531</v>
+        <v>-31.40587954317707</v>
       </c>
       <c r="F94">
-        <v>-3.049642195960513</v>
+        <v>-4.623133532884799</v>
       </c>
       <c r="G94">
-        <v>-4.378184384172322</v>
+        <v>-3.820708378632289</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.042542635535187</v>
       </c>
       <c r="E95">
-        <v>-34.48400333075182</v>
+        <v>-33.34647783086907</v>
       </c>
       <c r="F95">
-        <v>-3.250122018051244</v>
+        <v>-4.41362947630797</v>
       </c>
       <c r="G95">
-        <v>-4.042518240308998</v>
+        <v>-4.106640196859142</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.38450712416566</v>
       </c>
       <c r="E96">
-        <v>-37.84550090783054</v>
+        <v>-35.93063793792414</v>
       </c>
       <c r="F96">
-        <v>-3.375908779798946</v>
+        <v>-4.559582014109424</v>
       </c>
       <c r="G96">
-        <v>-4.870025513850764</v>
+        <v>-4.047874702991539</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.775012316487271</v>
       </c>
       <c r="E97">
-        <v>-37.91883954438477</v>
+        <v>-37.01607919400767</v>
       </c>
       <c r="F97">
-        <v>-3.167517220644077</v>
+        <v>-4.440361720763713</v>
       </c>
       <c r="G97">
-        <v>-5.218529953315381</v>
+        <v>-4.338639917705727</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.206017316349172</v>
       </c>
       <c r="E98">
-        <v>-40.64210078753344</v>
+        <v>-39.48729689507443</v>
       </c>
       <c r="F98">
-        <v>-3.568387401146036</v>
+        <v>-4.221815205617926</v>
       </c>
       <c r="G98">
-        <v>-5.495457087675415</v>
+        <v>-5.478298530145373</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.646603401216799</v>
       </c>
       <c r="E99">
-        <v>-43.7279093954992</v>
+        <v>-42.06926748494678</v>
       </c>
       <c r="F99">
-        <v>-3.377022105588308</v>
+        <v>-4.635250062885548</v>
       </c>
       <c r="G99">
-        <v>-5.687971931875113</v>
+        <v>-4.968272573819714</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.092173264200141</v>
       </c>
       <c r="E100">
-        <v>-45.65754877609264</v>
+        <v>-44.85270761918339</v>
       </c>
       <c r="F100">
-        <v>-3.182065008972042</v>
+        <v>-4.686337965718401</v>
       </c>
       <c r="G100">
-        <v>-6.776717664466307</v>
+        <v>-6.108441010272408</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.492465951656092</v>
       </c>
       <c r="E101">
-        <v>-47.14136215486793</v>
+        <v>-46.98253951447091</v>
       </c>
       <c r="F101">
-        <v>-3.063223279529411</v>
+        <v>-4.686028156309754</v>
       </c>
       <c r="G101">
-        <v>-6.648142696812092</v>
+        <v>-6.401953977784191</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.865776678207199</v>
       </c>
       <c r="E102">
-        <v>-50.04982892798231</v>
+        <v>-48.22303345634008</v>
       </c>
       <c r="F102">
-        <v>-3.052791648825957</v>
+        <v>-4.43914153557939</v>
       </c>
       <c r="G102">
-        <v>-7.541228566941281</v>
+        <v>-7.114042391644806</v>
       </c>
     </row>
   </sheetData>
